--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.68255711530718</v>
+        <v>8.885915531237417</v>
       </c>
       <c r="D2" t="n">
-        <v>54.64044457703014</v>
+        <v>8.879072243767398</v>
       </c>
       <c r="E2" t="n">
-        <v>11.33241536721676</v>
+        <v>1.841517497172724</v>
       </c>
       <c r="F2" t="n">
-        <v>11.38528626835718</v>
+        <v>1.850109018608041</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>27.80293459639872</v>
+        <v>4.517976871914793</v>
       </c>
       <c r="D3" t="n">
-        <v>27.67523685095767</v>
+        <v>4.497225988280621</v>
       </c>
       <c r="E3" t="n">
-        <v>11.33241536721676</v>
+        <v>1.841517497172724</v>
       </c>
       <c r="F3" t="n">
-        <v>11.38528626835718</v>
+        <v>1.850109018608041</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.5623293843672</v>
+        <v>6.591378524959669</v>
       </c>
       <c r="D4" t="n">
-        <v>40.57791744967016</v>
+        <v>6.593911585571401</v>
       </c>
       <c r="E4" t="n">
-        <v>11.33241536721676</v>
+        <v>1.841517497172724</v>
       </c>
       <c r="F4" t="n">
-        <v>11.38528626835718</v>
+        <v>1.850109018608041</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.42971164775072</v>
+        <v>8.194828142759492</v>
       </c>
       <c r="D5" t="n">
-        <v>50.48477932327468</v>
+        <v>8.203776640032135</v>
       </c>
       <c r="E5" t="n">
-        <v>11.33241536721676</v>
+        <v>1.841517497172724</v>
       </c>
       <c r="F5" t="n">
-        <v>11.38528626835718</v>
+        <v>1.850109018608041</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.94365770420059</v>
+        <v>5.190844376932596</v>
       </c>
       <c r="D6" t="n">
-        <v>32.27944488758808</v>
+        <v>5.245409794233063</v>
       </c>
       <c r="E6" t="n">
-        <v>11.33241536721676</v>
+        <v>1.841517497172724</v>
       </c>
       <c r="F6" t="n">
-        <v>11.38528626835718</v>
+        <v>1.850109018608041</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.07480503806023</v>
+        <v>7.649655818684787</v>
       </c>
       <c r="D7" t="n">
-        <v>46.92193199608153</v>
+        <v>7.624813949363248</v>
       </c>
       <c r="E7" t="n">
-        <v>11.33241536721676</v>
+        <v>1.841517497172724</v>
       </c>
       <c r="F7" t="n">
-        <v>11.38528626835718</v>
+        <v>1.850109018608041</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>61.89908847279071</v>
+        <v>10.05860187682849</v>
       </c>
       <c r="D8" t="n">
-        <v>62.29583365921624</v>
+        <v>10.12307296962264</v>
       </c>
       <c r="E8" t="n">
-        <v>11.33241536721676</v>
+        <v>1.841517497172724</v>
       </c>
       <c r="F8" t="n">
-        <v>11.38528626835718</v>
+        <v>1.850109018608041</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
